--- a/Data/Exports_Reports.xlsx
+++ b/Data/Exports_Reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB25D39-C789-49C1-94DE-71187DAAA5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64792DB-C5C0-4FDF-910B-1B44354D8F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exports_Reports" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Report Type</t>
   </si>
@@ -57,416 +57,17 @@
     <t>11 - MCX</t>
   </si>
   <si>
-    <t>15 - COTTON BALES</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">String </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>reportType</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getreportType(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>Exchange_ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getExchangeID(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>WSP_ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getWSP_ID1(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">); </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>WHID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getWHID1(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">String </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>COMMODITY_CODE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> =</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getCOMMODITY_CODE(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>CLIENT_ID_Export</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.getCLIENT_ID_Export(</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF0000C0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>dataRow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>);</t>
-    </r>
+    <t>De-pledge Request</t>
+  </si>
+  <si>
+    <t>Pledge Invocation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,22 +88,15 @@
       <family val="3"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF0000C0"/>
+      <color rgb="FF7F0055"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
     <font>
-      <i/>
       <sz val="10"/>
-      <color rgb="FF0000C0"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF7F0055"/>
+      <color rgb="FF646464"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -542,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -550,7 +144,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -833,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -874,7 +471,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -885,8 +482,8 @@
       <c r="D2" s="1">
         <v>1000421</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
+      <c r="E2" s="1">
+        <v>15</v>
       </c>
       <c r="F2" s="3">
         <v>100673000000011</v>
@@ -895,7 +492,9 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -905,7 +504,9 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -915,7 +516,9 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -935,7 +538,7 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -944,35 +547,53 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+    </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E12" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E13" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E14" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A14" s="6"/>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E16" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
